--- a/informes_data/Segunda FEB/2025-26/playoffs/individual/NP_play_by_play_2513090_ELIMINATORIAS14FINAL_PROCESSED.xlsx
+++ b/informes_data/Segunda FEB/2025-26/playoffs/individual/NP_play_by_play_2513090_ELIMINATORIAS14FINAL_PROCESSED.xlsx
@@ -565,67 +565,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>9.284800000000001</v>
+        <v>7.0441</v>
       </c>
       <c r="E2" t="n">
-        <v>6.1872</v>
+        <v>4.196</v>
       </c>
       <c r="F2" t="n">
-        <v>3.0977</v>
+        <v>2.8481</v>
       </c>
       <c r="G2" t="n">
-        <v>4.6985</v>
+        <v>4.7475</v>
       </c>
       <c r="H2" t="n">
-        <v>2.4565</v>
+        <v>2.5078</v>
       </c>
       <c r="I2" t="n">
-        <v>2.242</v>
+        <v>2.2396</v>
       </c>
       <c r="J2" t="n">
-        <v>3.743</v>
+        <v>3.826</v>
       </c>
       <c r="K2" t="n">
-        <v>1.8713</v>
+        <v>1.934</v>
       </c>
       <c r="L2" t="n">
-        <v>1.8717</v>
+        <v>1.892</v>
       </c>
       <c r="M2" t="n">
-        <v>0.9555</v>
+        <v>0.9215</v>
       </c>
       <c r="N2" t="n">
-        <v>0.5852000000000001</v>
+        <v>0.5738</v>
       </c>
       <c r="O2" t="n">
-        <v>0.3703</v>
+        <v>0.3477</v>
       </c>
       <c r="P2" t="n">
-        <v>0.2048</v>
+        <v>0.2025</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.0242</v>
+        <v>-1.0123</v>
       </c>
       <c r="R2" t="n">
-        <v>1.2291</v>
+        <v>1.2147</v>
       </c>
       <c r="S2" t="n">
-        <v>3.685</v>
+        <v>1.4058</v>
       </c>
       <c r="T2" t="n">
-        <v>3.4684</v>
+        <v>1.3823</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2166</v>
+        <v>0.0236</v>
       </c>
       <c r="V2" t="n">
-        <v>0.6965</v>
+        <v>0.6883</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>0.6965</v>
+        <v>0.6883</v>
       </c>
     </row>
     <row r="3">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.1571</v>
+        <v>4.1901</v>
       </c>
       <c r="E3" t="n">
-        <v>4.3389</v>
+        <v>4.4798</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.1818</v>
+        <v>-0.2897</v>
       </c>
       <c r="G3" t="n">
-        <v>2.3086</v>
+        <v>2.3141</v>
       </c>
       <c r="H3" t="n">
-        <v>2.4501</v>
+        <v>2.4511</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1414</v>
+        <v>-0.137</v>
       </c>
       <c r="J3" t="n">
-        <v>3.9147</v>
+        <v>3.9919</v>
       </c>
       <c r="K3" t="n">
-        <v>2.8687</v>
+        <v>2.904</v>
       </c>
       <c r="L3" t="n">
-        <v>1.0459</v>
+        <v>1.0879</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.606</v>
+        <v>-1.6777</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.4186</v>
+        <v>-0.4529</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.1874</v>
+        <v>-1.2248</v>
       </c>
       <c r="P3" t="n">
-        <v>1.0242</v>
+        <v>1.0123</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.2048</v>
+        <v>-0.2025</v>
       </c>
       <c r="R3" t="n">
-        <v>1.2291</v>
+        <v>1.2147</v>
       </c>
       <c r="S3" t="n">
-        <v>0.6884</v>
+        <v>0.706</v>
       </c>
       <c r="T3" t="n">
-        <v>0.4933</v>
+        <v>0.5327</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1951</v>
+        <v>0.1733</v>
       </c>
       <c r="V3" t="n">
-        <v>0.1359</v>
+        <v>0.1577</v>
       </c>
       <c r="W3" t="n">
-        <v>0.1359</v>
+        <v>0.1577</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.4973</v>
+        <v>4.086</v>
       </c>
       <c r="E4" t="n">
-        <v>2.8839</v>
+        <v>3.9668</v>
       </c>
       <c r="F4" t="n">
-        <v>0.6133999999999999</v>
+        <v>0.1192</v>
       </c>
       <c r="G4" t="n">
-        <v>2.8075</v>
+        <v>2.8397</v>
       </c>
       <c r="H4" t="n">
-        <v>0.4574</v>
+        <v>0.4736</v>
       </c>
       <c r="I4" t="n">
-        <v>2.3501</v>
+        <v>2.3661</v>
       </c>
       <c r="J4" t="n">
-        <v>4.0461</v>
+        <v>4.1401</v>
       </c>
       <c r="K4" t="n">
-        <v>1.1825</v>
+        <v>1.2235</v>
       </c>
       <c r="L4" t="n">
-        <v>2.8636</v>
+        <v>2.9166</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.2386</v>
+        <v>-1.3003</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.7251</v>
+        <v>-0.7499</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.5135</v>
+        <v>-0.5505</v>
       </c>
       <c r="P4" t="n">
-        <v>0.6145</v>
+        <v>0.6074000000000001</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.0242</v>
+        <v>-1.0123</v>
       </c>
       <c r="R4" t="n">
-        <v>1.6388</v>
+        <v>1.6196</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3173</v>
+        <v>0.8898</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.138</v>
+        <v>0.839</v>
       </c>
       <c r="U4" t="n">
-        <v>0.4553</v>
+        <v>0.0509</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.2421</v>
+        <v>-0.2509</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.2421</v>
+        <v>-0.2509</v>
       </c>
     </row>
     <row r="5">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.7946</v>
+        <v>1.97</v>
       </c>
       <c r="E5" t="n">
-        <v>2.0767</v>
+        <v>2.3401</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.282</v>
+        <v>-0.3701</v>
       </c>
       <c r="G5" t="n">
         <v>0.2574</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8751</v>
+        <v>0.87</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.6177</v>
+        <v>-0.6126</v>
       </c>
       <c r="J5" t="n">
-        <v>1.468</v>
+        <v>1.5188</v>
       </c>
       <c r="K5" t="n">
-        <v>1.0148</v>
+        <v>1.0273</v>
       </c>
       <c r="L5" t="n">
-        <v>0.4532</v>
+        <v>0.4915</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.2106</v>
+        <v>-1.2614</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.1396</v>
+        <v>-0.1572</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.0709</v>
+        <v>-1.1041</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.0242</v>
+        <v>-1.0123</v>
       </c>
       <c r="R5" t="n">
-        <v>1.0242</v>
+        <v>1.0123</v>
       </c>
       <c r="S5" t="n">
-        <v>0.008399999999999999</v>
+        <v>0.1782</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.138</v>
+        <v>0.0482</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1464</v>
+        <v>0.13</v>
       </c>
       <c r="V5" t="n">
-        <v>1.5288</v>
+        <v>1.5344</v>
       </c>
       <c r="W5" t="n">
-        <v>1.7709</v>
+        <v>1.7853</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.2421</v>
+        <v>-0.2509</v>
       </c>
     </row>
     <row r="6">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.2619</v>
+        <v>0.7059</v>
       </c>
       <c r="E6" t="n">
-        <v>1.369</v>
+        <v>1.0602</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.1072</v>
+        <v>-0.3544</v>
       </c>
       <c r="G6" t="n">
-        <v>0.865</v>
+        <v>0.845</v>
       </c>
       <c r="H6" t="n">
-        <v>0.6382</v>
+        <v>0.6328</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2268</v>
+        <v>0.2121</v>
       </c>
       <c r="J6" t="n">
-        <v>0.2947</v>
+        <v>0.2973</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1366</v>
+        <v>0.1383</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1581</v>
+        <v>0.159</v>
       </c>
       <c r="M6" t="n">
-        <v>0.5703</v>
+        <v>0.5477</v>
       </c>
       <c r="N6" t="n">
-        <v>0.5016</v>
+        <v>0.4945</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0687</v>
+        <v>0.0531</v>
       </c>
       <c r="P6" t="n">
-        <v>0.8194</v>
+        <v>0.8098</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.8194</v>
+        <v>0.8098</v>
       </c>
       <c r="S6" t="n">
-        <v>1.2422</v>
+        <v>0.7432</v>
       </c>
       <c r="T6" t="n">
-        <v>1.0744</v>
+        <v>0.7629</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1678</v>
+        <v>-0.0198</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.6647</v>
+        <v>-1.6921</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.6647</v>
+        <v>-1.6921</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. LATORRE SANCHEZ</t>
+          <t>N. DEDOVIC</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.3346</v>
+        <v>0.3169</v>
       </c>
       <c r="E7" t="n">
-        <v>0.7036</v>
+        <v>-1.1374</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.0382</v>
+        <v>1.4543</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.5105</v>
+        <v>-1.9642</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.2586</v>
+        <v>0.5744</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.2519</v>
+        <v>-2.5385</v>
       </c>
       <c r="J7" t="n">
-        <v>0.4807</v>
+        <v>-2.3723</v>
       </c>
       <c r="K7" t="n">
-        <v>0.2436</v>
+        <v>0.2371</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2371</v>
+        <v>-2.6093</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.9912</v>
+        <v>0.4081</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.5022</v>
+        <v>0.3373</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.489</v>
+        <v>0.0708</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.4097</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.2291</v>
+        <v>-1.2147</v>
       </c>
       <c r="R7" t="n">
-        <v>0.8194</v>
+        <v>1.2147</v>
       </c>
       <c r="S7" t="n">
-        <v>1.8276</v>
+        <v>0.4958</v>
       </c>
       <c r="T7" t="n">
-        <v>1.452</v>
+        <v>0.6643</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3756</v>
+        <v>-0.1685</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.2421</v>
+        <v>1.7853</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.7853</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.2421</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1033,58 +1033,58 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.5542</v>
+        <v>0.2027</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.7667</v>
+        <v>-1.1835</v>
       </c>
       <c r="F8" t="n">
-        <v>1.2124</v>
+        <v>1.3863</v>
       </c>
       <c r="G8" t="n">
-        <v>0.3813</v>
+        <v>0.4031</v>
       </c>
       <c r="H8" t="n">
-        <v>-2.0958</v>
+        <v>-2.0765</v>
       </c>
       <c r="I8" t="n">
-        <v>2.477</v>
+        <v>2.4796</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.2268</v>
+        <v>-0.1885</v>
       </c>
       <c r="K8" t="n">
-        <v>-2.1235</v>
+        <v>-2.0967</v>
       </c>
       <c r="L8" t="n">
-        <v>1.8967</v>
+        <v>1.9082</v>
       </c>
       <c r="M8" t="n">
-        <v>0.6081</v>
+        <v>0.5915</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0278</v>
+        <v>0.0202</v>
       </c>
       <c r="O8" t="n">
-        <v>0.5803</v>
+        <v>0.5714</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.0242</v>
+        <v>-1.0123</v>
       </c>
       <c r="R8" t="n">
-        <v>1.0242</v>
+        <v>1.0123</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.9355</v>
+        <v>-0.2003</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.5155999999999999</v>
+        <v>0.0172</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.4199</v>
+        <v>-0.2175</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>N. DEDOVIC</t>
+          <t>A. LATORRE SANCHEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.0719</v>
+        <v>-1.2957</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.3031</v>
+        <v>-0.013</v>
       </c>
       <c r="F9" t="n">
-        <v>1.2312</v>
+        <v>-1.2827</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.9412</v>
+        <v>-1.5003</v>
       </c>
       <c r="H9" t="n">
-        <v>0.5961</v>
+        <v>-0.2194</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.5374</v>
+        <v>-1.2809</v>
       </c>
       <c r="J9" t="n">
-        <v>-2.3948</v>
+        <v>0.5513</v>
       </c>
       <c r="K9" t="n">
-        <v>0.2342</v>
+        <v>0.3127</v>
       </c>
       <c r="L9" t="n">
-        <v>-2.629</v>
+        <v>0.2385</v>
       </c>
       <c r="M9" t="n">
-        <v>0.4536</v>
+        <v>-2.0516</v>
       </c>
       <c r="N9" t="n">
-        <v>0.362</v>
+        <v>-0.5322</v>
       </c>
       <c r="O9" t="n">
-        <v>0.0916</v>
+        <v>-1.5194</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>-0.4049</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.2291</v>
+        <v>-1.2147</v>
       </c>
       <c r="R9" t="n">
-        <v>1.2291</v>
+        <v>0.8098</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.9016</v>
+        <v>0.8604000000000001</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4501</v>
+        <v>0.6504</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.4515</v>
+        <v>0.21</v>
       </c>
       <c r="V9" t="n">
-        <v>1.7709</v>
+        <v>-0.2509</v>
       </c>
       <c r="W9" t="n">
-        <v>1.7709</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-0.2509</v>
       </c>
     </row>
     <row r="10">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.2951</v>
+        <v>-2.0209</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.973</v>
+        <v>-1.5018</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.3221</v>
+        <v>-0.5191</v>
       </c>
       <c r="G10" t="n">
-        <v>0.4727</v>
+        <v>0.4962</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.3592</v>
+        <v>-0.3372</v>
       </c>
       <c r="I10" t="n">
-        <v>0.8319</v>
+        <v>0.8334</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.0318</v>
+        <v>0.0314</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.1673</v>
+        <v>-1.1287</v>
       </c>
       <c r="L10" t="n">
-        <v>1.1355</v>
+        <v>1.1601</v>
       </c>
       <c r="M10" t="n">
-        <v>0.5044999999999999</v>
+        <v>0.4648</v>
       </c>
       <c r="N10" t="n">
-        <v>0.8081</v>
+        <v>0.7915</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.3035</v>
+        <v>-0.3267</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.8194</v>
+        <v>-0.8098</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.2291</v>
+        <v>-1.2147</v>
       </c>
       <c r="R10" t="n">
-        <v>0.4097</v>
+        <v>0.4049</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.1775</v>
+        <v>0.0779</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.7121</v>
+        <v>-0.3185</v>
       </c>
       <c r="U10" t="n">
-        <v>0.5346</v>
+        <v>0.3965</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.7709</v>
+        <v>-1.7853</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.7709</v>
+        <v>-1.7853</v>
       </c>
     </row>
     <row r="11">
@@ -1267,64 +1267,64 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.3954</v>
+        <v>-2.2065</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.2099</v>
+        <v>-0.4324</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.1855</v>
+        <v>-1.7741</v>
       </c>
       <c r="G11" t="n">
-        <v>-4.5992</v>
+        <v>-4.6006</v>
       </c>
       <c r="H11" t="n">
-        <v>-3.2246</v>
+        <v>-3.2034</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.3746</v>
+        <v>-1.3972</v>
       </c>
       <c r="J11" t="n">
-        <v>-2.3752</v>
+        <v>-2.3076</v>
       </c>
       <c r="K11" t="n">
-        <v>-3.1405</v>
+        <v>-3.0864</v>
       </c>
       <c r="L11" t="n">
-        <v>0.7653</v>
+        <v>0.7788</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.2241</v>
+        <v>-2.293</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.08409999999999999</v>
+        <v>-0.1169</v>
       </c>
       <c r="O11" t="n">
-        <v>-2.1399</v>
+        <v>-2.1761</v>
       </c>
       <c r="P11" t="n">
-        <v>0.6145</v>
+        <v>0.6074000000000001</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.2048</v>
+        <v>-0.2025</v>
       </c>
       <c r="R11" t="n">
-        <v>0.8194</v>
+        <v>0.8098</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.5913</v>
+        <v>0.5965</v>
       </c>
       <c r="T11" t="n">
-        <v>0.1895</v>
+        <v>0.8875</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.7808</v>
+        <v>-0.2909</v>
       </c>
       <c r="V11" t="n">
-        <v>1.1806</v>
+        <v>1.1902</v>
       </c>
       <c r="W11" t="n">
-        <v>1.1806</v>
+        <v>1.1902</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>12.3445</v>
+        <v>12.9926</v>
       </c>
       <c r="E12" t="n">
-        <v>10.3066</v>
+        <v>11.7748</v>
       </c>
       <c r="F12" t="n">
-        <v>2.0379</v>
+        <v>1.2178</v>
       </c>
       <c r="G12" t="n">
-        <v>3.740100000000002</v>
+        <v>3.837899999999999</v>
       </c>
       <c r="H12" t="n">
-        <v>1.535199999999999</v>
+        <v>1.673200000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>2.2048</v>
+        <v>2.1646</v>
       </c>
       <c r="J12" t="n">
-        <v>8.918600000000001</v>
+        <v>9.488400000000002</v>
       </c>
       <c r="K12" t="n">
-        <v>1.120400000000001</v>
+        <v>1.4651</v>
       </c>
       <c r="L12" t="n">
-        <v>7.7981</v>
+        <v>8.023299999999999</v>
       </c>
       <c r="M12" t="n">
-        <v>-5.1785</v>
+        <v>-5.6504</v>
       </c>
       <c r="N12" t="n">
-        <v>0.4151000000000001</v>
+        <v>0.2081999999999999</v>
       </c>
       <c r="O12" t="n">
-        <v>-5.5933</v>
+        <v>-5.8586</v>
       </c>
       <c r="P12" t="n">
-        <v>2.0483</v>
+        <v>2.0247</v>
       </c>
       <c r="Q12" t="n">
-        <v>-8.1937</v>
+        <v>-8.0983</v>
       </c>
       <c r="R12" t="n">
-        <v>10.2424</v>
+        <v>10.1226</v>
       </c>
       <c r="S12" t="n">
-        <v>5.163</v>
+        <v>5.753299999999999</v>
       </c>
       <c r="T12" t="n">
-        <v>4.7238</v>
+        <v>5.466</v>
       </c>
       <c r="U12" t="n">
-        <v>0.4391999999999997</v>
+        <v>0.2876</v>
       </c>
       <c r="V12" t="n">
-        <v>1.3929</v>
+        <v>1.3767</v>
       </c>
       <c r="W12" t="n">
-        <v>4.8583</v>
+        <v>4.9185</v>
       </c>
       <c r="X12" t="n">
-        <v>-3.4654</v>
+        <v>-3.5418</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.6741</v>
+        <v>4.8107</v>
       </c>
       <c r="E13" t="n">
-        <v>5.4345</v>
+        <v>6.2852</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.7603</v>
+        <v>-1.4745</v>
       </c>
       <c r="G13" t="n">
-        <v>5.571</v>
+        <v>5.584</v>
       </c>
       <c r="H13" t="n">
-        <v>2.0064</v>
+        <v>1.9782</v>
       </c>
       <c r="I13" t="n">
-        <v>3.5646</v>
+        <v>3.6058</v>
       </c>
       <c r="J13" t="n">
-        <v>6.1458</v>
+        <v>6.2336</v>
       </c>
       <c r="K13" t="n">
-        <v>0.9758</v>
+        <v>0.9877</v>
       </c>
       <c r="L13" t="n">
-        <v>5.17</v>
+        <v>5.2459</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.5748</v>
+        <v>-0.6497000000000001</v>
       </c>
       <c r="N13" t="n">
-        <v>1.0307</v>
+        <v>0.9903999999999999</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.6054</v>
+        <v>-1.6401</v>
       </c>
       <c r="P13" t="n">
-        <v>0.4097</v>
+        <v>0.4049</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.2048</v>
+        <v>-0.2025</v>
       </c>
       <c r="R13" t="n">
-        <v>0.6145</v>
+        <v>0.6074000000000001</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.7163</v>
+        <v>-0.5831</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.0968</v>
+        <v>-0.3411</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.6195000000000001</v>
+        <v>-0.242</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.5903</v>
+        <v>-0.5951</v>
       </c>
       <c r="W13" t="n">
-        <v>0.5903</v>
+        <v>0.5951</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.1806</v>
+        <v>-1.1902</v>
       </c>
     </row>
     <row r="14">
@@ -1501,64 +1501,64 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.6112</v>
+        <v>0.3432</v>
       </c>
       <c r="E14" t="n">
-        <v>0.6925</v>
+        <v>0.2373</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.08119999999999999</v>
+        <v>0.1059</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.5165999999999999</v>
+        <v>-0.5656</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.2567</v>
+        <v>-0.2758</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.2598</v>
+        <v>-0.2899</v>
       </c>
       <c r="J14" t="n">
-        <v>0.2434</v>
+        <v>0.2579</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.0332</v>
+        <v>-0.0204</v>
       </c>
       <c r="L14" t="n">
-        <v>0.2766</v>
+        <v>0.2783</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.7599</v>
+        <v>-0.8235</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.2235</v>
+        <v>-0.2553</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.5364</v>
+        <v>-0.5682</v>
       </c>
       <c r="P14" t="n">
-        <v>0.6145</v>
+        <v>0.6074000000000001</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.2048</v>
+        <v>-0.2025</v>
       </c>
       <c r="R14" t="n">
-        <v>0.8194</v>
+        <v>0.8098</v>
       </c>
       <c r="S14" t="n">
-        <v>0.4836</v>
+        <v>0.2371</v>
       </c>
       <c r="T14" t="n">
-        <v>0.6243</v>
+        <v>0.1174</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.1407</v>
+        <v>0.1196</v>
       </c>
       <c r="V14" t="n">
-        <v>0.0297</v>
+        <v>0.0645</v>
       </c>
       <c r="W14" t="n">
-        <v>0.0297</v>
+        <v>0.0645</v>
       </c>
       <c r="X14" t="n">
         <v>0</v>
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.4022</v>
+        <v>-0.075</v>
       </c>
       <c r="E15" t="n">
-        <v>3.1483</v>
+        <v>2.453</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.746</v>
+        <v>-2.528</v>
       </c>
       <c r="G15" t="n">
-        <v>0.4843</v>
+        <v>0.4671</v>
       </c>
       <c r="H15" t="n">
-        <v>1.5887</v>
+        <v>1.5817</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.1043</v>
+        <v>-1.1146</v>
       </c>
       <c r="J15" t="n">
-        <v>2.3442</v>
+        <v>2.3718</v>
       </c>
       <c r="K15" t="n">
-        <v>2.1467</v>
+        <v>2.173</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1976</v>
+        <v>0.1988</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.8599</v>
+        <v>-1.9047</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.5580000000000001</v>
+        <v>-0.5913</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.3019</v>
+        <v>-1.3134</v>
       </c>
       <c r="P15" t="n">
-        <v>0.6145</v>
+        <v>0.6074000000000001</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>0.6145</v>
+        <v>0.6074000000000001</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.2125</v>
+        <v>-0.6476</v>
       </c>
       <c r="T15" t="n">
-        <v>0.804</v>
+        <v>0.08119999999999999</v>
       </c>
       <c r="U15" t="n">
-        <v>-1.0166</v>
+        <v>-0.7288</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.4841</v>
+        <v>-0.5019</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.4841</v>
+        <v>-0.5019</v>
       </c>
     </row>
     <row r="16">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-2.0159</v>
+        <v>-0.9163</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.0016</v>
+        <v>1.1158</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.0143</v>
+        <v>-2.0321</v>
       </c>
       <c r="G16" t="n">
-        <v>0.8818</v>
+        <v>0.8947000000000001</v>
       </c>
       <c r="H16" t="n">
-        <v>-2.4894</v>
+        <v>-2.5094</v>
       </c>
       <c r="I16" t="n">
-        <v>3.3712</v>
+        <v>3.4041</v>
       </c>
       <c r="J16" t="n">
-        <v>1.9259</v>
+        <v>2.0351</v>
       </c>
       <c r="K16" t="n">
-        <v>-2.0982</v>
+        <v>-2.0578</v>
       </c>
       <c r="L16" t="n">
-        <v>4.0241</v>
+        <v>4.093</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.0441</v>
+        <v>-1.1404</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.3912</v>
+        <v>-0.4516</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.6529</v>
+        <v>-0.6889</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.6145</v>
+        <v>-0.6074000000000001</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.2533</v>
+        <v>-2.227</v>
       </c>
       <c r="R16" t="n">
-        <v>1.6388</v>
+        <v>1.6196</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.9349</v>
+        <v>-0.8595</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.0968</v>
+        <v>-0.1335</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.8381</v>
+        <v>-0.7259</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.3482</v>
+        <v>-0.3442</v>
       </c>
       <c r="W16" t="n">
-        <v>1.4227</v>
+        <v>1.4411</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.7709</v>
+        <v>-1.7853</v>
       </c>
     </row>
     <row r="17">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-2.4147</v>
+        <v>-1.9005</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.0238</v>
+        <v>0.5528999999999999</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.391</v>
+        <v>-2.4535</v>
       </c>
       <c r="G17" t="n">
-        <v>1.3593</v>
+        <v>1.3509</v>
       </c>
       <c r="H17" t="n">
-        <v>0.7105</v>
+        <v>0.6928</v>
       </c>
       <c r="I17" t="n">
-        <v>0.6489</v>
+        <v>0.6581</v>
       </c>
       <c r="J17" t="n">
-        <v>3.2724</v>
+        <v>3.3633</v>
       </c>
       <c r="K17" t="n">
-        <v>1.4362</v>
+        <v>1.4803</v>
       </c>
       <c r="L17" t="n">
-        <v>1.8362</v>
+        <v>1.883</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.9131</v>
+        <v>-2.0124</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.7257</v>
+        <v>-0.7875</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.1874</v>
+        <v>-1.2248</v>
       </c>
       <c r="P17" t="n">
-        <v>-1.8436</v>
+        <v>-1.8221</v>
       </c>
       <c r="Q17" t="n">
-        <v>-3.2776</v>
+        <v>-3.2392</v>
       </c>
       <c r="R17" t="n">
-        <v>1.4339</v>
+        <v>1.4172</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.7498</v>
+        <v>-0.2392</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.2606</v>
+        <v>0.1779</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.4892</v>
+        <v>-0.4171</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.1806</v>
+        <v>-1.1902</v>
       </c>
       <c r="W17" t="n">
-        <v>0.2421</v>
+        <v>0.2509</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.4227</v>
+        <v>-1.4411</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. ECHEVERRIA FERNANDEZ</t>
+          <t>J. SANTANO BARTOLOME</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,58 +1813,58 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.5306</v>
+        <v>-2.1366</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.5399</v>
+        <v>-1.5289</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.9907</v>
+        <v>-0.6077</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.9298999999999999</v>
+        <v>-1.7023</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.6971000000000001</v>
+        <v>-1.857</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.2329</v>
+        <v>0.1547</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.6968</v>
+        <v>-0.4543</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.6968</v>
+        <v>-0.5736</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>0.1193</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.2332</v>
+        <v>-1.248</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.0003</v>
+        <v>-1.2834</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.2329</v>
+        <v>0.0354</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.0242</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.0242</v>
+        <v>-1.0123</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.0123</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.5764</v>
+        <v>-0.4343</v>
       </c>
       <c r="T18" t="n">
-        <v>0.1811</v>
+        <v>-0.0624</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.7575</v>
+        <v>-0.3719</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. SANTANO BARTOLOME</t>
+          <t>M. ECHEVERRIA FERNANDEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,58 +1891,58 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.5633</v>
+        <v>-2.5858</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.87</v>
+        <v>-1.8256</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.6933</v>
+        <v>-0.7602</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.6701</v>
+        <v>-0.9523</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.8344</v>
+        <v>-0.7109</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1644</v>
+        <v>-0.2414</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.4611</v>
+        <v>-0.6921</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.5797</v>
+        <v>-0.6921</v>
       </c>
       <c r="L19" t="n">
-        <v>0.1185</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.2089</v>
+        <v>-0.2602</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.2548</v>
+        <v>-0.0188</v>
       </c>
       <c r="O19" t="n">
-        <v>0.0458</v>
+        <v>-0.2414</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>-1.0123</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.0242</v>
+        <v>-1.0123</v>
       </c>
       <c r="R19" t="n">
-        <v>1.0242</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.8932</v>
+        <v>-0.6212</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.3846</v>
+        <v>-0.1213</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.5086000000000001</v>
+        <v>-0.5</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,58 +1969,58 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.5973</v>
+        <v>-3.3197</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.5761</v>
+        <v>-3.6073</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.0212</v>
+        <v>0.2876</v>
       </c>
       <c r="G20" t="n">
-        <v>-3.804</v>
+        <v>-3.7856</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.0087</v>
+        <v>-0.9893</v>
       </c>
       <c r="I20" t="n">
-        <v>-2.7953</v>
+        <v>-2.7962</v>
       </c>
       <c r="J20" t="n">
-        <v>-3.4953</v>
+        <v>-3.4376</v>
       </c>
       <c r="K20" t="n">
-        <v>-2.2348</v>
+        <v>-2.1961</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.2605</v>
+        <v>-1.2414</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.3087</v>
+        <v>-0.348</v>
       </c>
       <c r="N20" t="n">
-        <v>1.2261</v>
+        <v>1.2068</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.5348</v>
+        <v>-1.5548</v>
       </c>
       <c r="P20" t="n">
-        <v>0.4097</v>
+        <v>0.4049</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.4097</v>
+        <v>0.4049</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.203</v>
+        <v>0.061</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.0809</v>
+        <v>-0.1698</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1222</v>
+        <v>0.2307</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,64 +2047,64 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.9103</v>
+        <v>-4.4958</v>
       </c>
       <c r="E21" t="n">
-        <v>-4.3018</v>
+        <v>-4.9001</v>
       </c>
       <c r="F21" t="n">
-        <v>0.3915</v>
+        <v>0.4042</v>
       </c>
       <c r="G21" t="n">
-        <v>-5.116</v>
+        <v>-5.1288</v>
       </c>
       <c r="H21" t="n">
-        <v>0.4455</v>
+        <v>0.4166</v>
       </c>
       <c r="I21" t="n">
-        <v>-5.5615</v>
+        <v>-5.5454</v>
       </c>
       <c r="J21" t="n">
-        <v>-4.0999</v>
+        <v>-4.0274</v>
       </c>
       <c r="K21" t="n">
-        <v>0.6693</v>
+        <v>0.6908</v>
       </c>
       <c r="L21" t="n">
-        <v>-4.7692</v>
+        <v>-4.7181</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.016</v>
+        <v>-1.1015</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.2238</v>
+        <v>-0.2742</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.7922</v>
+        <v>-0.8273</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.6145</v>
+        <v>-0.6074000000000001</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.2533</v>
+        <v>-2.227</v>
       </c>
       <c r="R21" t="n">
-        <v>1.6388</v>
+        <v>1.6196</v>
       </c>
       <c r="S21" t="n">
-        <v>0.6395999999999999</v>
+        <v>0.0501</v>
       </c>
       <c r="T21" t="n">
-        <v>0.8709</v>
+        <v>0.164</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2313</v>
+        <v>-0.1139</v>
       </c>
       <c r="V21" t="n">
-        <v>1.1806</v>
+        <v>1.1902</v>
       </c>
       <c r="W21" t="n">
-        <v>1.1806</v>
+        <v>1.1902</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-12.3446</v>
+        <v>-10.2758</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.0379</v>
+        <v>-1.2177</v>
       </c>
       <c r="F22" t="n">
-        <v>-10.3065</v>
+        <v>-9.058300000000001</v>
       </c>
       <c r="G22" t="n">
-        <v>-3.7402</v>
+        <v>-3.837899999999999</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.535199999999999</v>
+        <v>-1.6731</v>
       </c>
       <c r="I22" t="n">
-        <v>-2.2047</v>
+        <v>-2.1648</v>
       </c>
       <c r="J22" t="n">
-        <v>5.178600000000001</v>
+        <v>5.6503</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.4146999999999996</v>
+        <v>-0.2081999999999998</v>
       </c>
       <c r="L22" t="n">
-        <v>5.593300000000001</v>
+        <v>5.858799999999999</v>
       </c>
       <c r="M22" t="n">
-        <v>-8.9186</v>
+        <v>-9.4884</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.1205</v>
+        <v>-1.4649</v>
       </c>
       <c r="O22" t="n">
-        <v>-7.798100000000001</v>
+        <v>-8.023499999999999</v>
       </c>
       <c r="P22" t="n">
-        <v>-2.0484</v>
+        <v>-2.0246</v>
       </c>
       <c r="Q22" t="n">
-        <v>-10.2422</v>
+        <v>-10.1228</v>
       </c>
       <c r="R22" t="n">
-        <v>8.1938</v>
+        <v>8.0982</v>
       </c>
       <c r="S22" t="n">
-        <v>-5.1629</v>
+        <v>-3.0367</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.4394</v>
+        <v>-0.2876000000000001</v>
       </c>
       <c r="U22" t="n">
-        <v>-4.7237</v>
+        <v>-2.7493</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.3929</v>
+        <v>-1.3767</v>
       </c>
       <c r="W22" t="n">
-        <v>3.4654</v>
+        <v>3.5418</v>
       </c>
       <c r="X22" t="n">
-        <v>-4.8583</v>
+        <v>-4.9185</v>
       </c>
     </row>
   </sheetData>
